--- a/output/勤務表_2026年5月.xlsx
+++ b/output/勤務表_2026年5月.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF38"/>
+  <dimension ref="A1:AF37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -863,142 +863,142 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>準</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>深</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>準</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>早</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>早</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>深</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>準</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>深</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>深</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>早</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>深</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>準</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>早</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>深</t>
+          <t>日</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
     </row>
@@ -1010,157 +1010,157 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>深</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>早</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>深</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>準</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>早</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>深</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>早</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>深</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>深</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>準</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>深</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>深</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
         <is>
           <t>早</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>深</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>準</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>早</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>深</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>準</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>早</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>休</t>
         </is>
       </c>
     </row>
@@ -1172,157 +1172,157 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>準</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>準</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>早</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>深</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>早</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>深</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>準</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
         <is>
           <t>早</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>深</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>事務</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>準</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>早</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>深</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
         <is>
           <t>準</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>早</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>深</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1374,12 +1374,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1394,22 +1394,22 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1459,22 +1459,22 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>P</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>休</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1516,12 +1516,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>休</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>P</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>P</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1576,17 +1576,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>P</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1596,49 +1596,49 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
           <t>P</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
       <c r="AE8" t="inlineStr">
         <is>
           <t>休</t>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
     </row>
@@ -1683,27 +1683,27 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>準</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>深</t>
+          <t>休</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>早</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1718,87 +1718,87 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>準</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
           <t>早</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>深</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>準</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
           <t>準</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>準</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
         <is>
           <t>早</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>深</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>準</t>
+          <t>日</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -1820,147 +1820,147 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>早</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>深</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>深</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>準</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
           <t>早</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
         <is>
           <t>深</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>準</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
         <is>
           <t>深</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>早</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>準</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>深</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
       <c r="X10" t="inlineStr">
         <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
           <t>早</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>準</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>休</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -1982,12 +1982,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>早</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2007,132 +2007,132 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>深</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>深</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>準</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>深</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>早</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>早</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
         <is>
           <t>深</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>準</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
         <is>
           <t>早</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
         <is>
           <t>深</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>準</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>早</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>深</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>準</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>休</t>
         </is>
       </c>
     </row>
@@ -2169,112 +2169,112 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>早</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
+          <t>準</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>深</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>準</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
           <t>早</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>準</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>深</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
         <is>
           <t>早</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>準</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>深</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>早</t>
+          <t>日</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>準</t>
+          <t>休</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2289,12 +2289,12 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>深</t>
+          <t>休</t>
         </is>
       </c>
     </row>
@@ -2321,44 +2321,44 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t>休</t>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>休</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2528,12 +2528,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>日</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2553,12 +2553,12 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>P</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2573,17 +2573,17 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>休</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
     </row>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>準</t>
+          <t>日</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>準</t>
+          <t>早</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -3034,44 +3034,44 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
           <t>早</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>深</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>準</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
       <c r="Z17" t="inlineStr">
         <is>
           <t>日</t>
@@ -3079,12 +3079,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>早</t>
+          <t>休</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>深</t>
+          <t>休</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -3094,17 +3094,17 @@
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>準</t>
+          <t>休</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -3181,17 +3181,17 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -3221,17 +3221,17 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3266,14 +3266,14 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>阿瀬真希</t>
+          <t>石橋泉子</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -3428,14 +3428,14 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>石橋泉子</t>
+          <t>川野藍</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3450,19 +3450,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>休</t>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -3505,29 +3505,29 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
       <c r="T20" t="inlineStr">
         <is>
           <t>休</t>
@@ -3535,32 +3535,32 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>A</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3570,22 +3570,22 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>休</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -3597,12 +3597,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>川野藍</t>
+          <t>工藤泉</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3617,22 +3617,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3647,27 +3647,27 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>休</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>日</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3677,7 +3677,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>休</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -3687,27 +3687,27 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>日</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>日</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>休</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>休</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>休</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>日</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
@@ -3752,14 +3752,14 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>休</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>工藤泉</t>
+          <t>曽我久美子</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>P</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3804,12 +3804,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -3819,17 +3819,17 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>P</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>P</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -3879,22 +3879,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3909,39 +3909,39 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>曽我久美子</t>
+          <t>中嶋桜月</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>休</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>休</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>日</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
@@ -4076,19 +4076,19 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>休</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>中嶋桜月</t>
+          <t>石田美歩</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>深</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>準</t>
+          <t>休</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>早</t>
+          <t>休</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>深</t>
+          <t>休</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -4173,17 +4173,17 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>準</t>
+          <t>休</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>A</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>早</t>
+          <t>休</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>深</t>
+          <t>休</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>準</t>
+          <t>休</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>早</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
@@ -4238,19 +4238,19 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>早</t>
+          <t>休</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>石田美歩</t>
+          <t>堀太</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>休</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4260,17 +4260,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>送迎</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>送迎</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>休</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -4280,12 +4280,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>送迎</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>休</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -4295,17 +4295,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>送迎</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>送迎</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>休</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -4315,12 +4315,12 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>送迎</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>休</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -4330,17 +4330,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>送迎</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>送迎</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>休</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>送迎</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>休</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -4365,17 +4365,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>送迎</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>送迎</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>休</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>送迎</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>休</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
@@ -4400,19 +4400,19 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>送迎</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>堀太</t>
+          <t>今井順子</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>皿洗い</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4422,17 +4422,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>送迎</t>
+          <t>皿洗い</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>送迎</t>
+          <t>休</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>皿洗い</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>送迎</t>
+          <t>休</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -4457,17 +4457,17 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>送迎</t>
+          <t>皿洗い</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>送迎</t>
+          <t>休</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>皿洗い</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>送迎</t>
+          <t>休</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -4492,12 +4492,12 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>送迎</t>
+          <t>皿洗い</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>送迎</t>
+          <t>休</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>皿洗い</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>送迎</t>
+          <t>休</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -4527,17 +4527,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>送迎</t>
+          <t>皿洗い</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>送迎</t>
+          <t>休</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>皿洗い</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>送迎</t>
+          <t>皿洗い</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -4557,51 +4557,51 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>皿洗い</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>送迎</t>
+          <t>休</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>今井順子</t>
+          <t>永井仁美</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>皿洗い</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t>皿洗い</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>休</t>
@@ -4614,19 +4614,19 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
           <t>皿洗い</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
       <c r="M27" t="inlineStr">
         <is>
           <t>休</t>
@@ -4654,14 +4654,14 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
           <t>皿洗い</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
       <c r="T27" t="inlineStr">
         <is>
           <t>休</t>
@@ -4669,14 +4669,14 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
           <t>皿洗い</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
       <c r="W27" t="inlineStr">
         <is>
           <t>休</t>
@@ -4694,32 +4694,32 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>皿洗い</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
           <t>皿洗い</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
       <c r="AC27" t="inlineStr">
         <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
           <t>皿洗い</t>
         </is>
       </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>皿洗い</t>
+          <t>休</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
@@ -4731,7 +4731,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>永井仁美</t>
+          <t>石橋睦子</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4741,69 +4741,69 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
           <t>皿洗い</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
         <is>
           <t>皿洗い</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>皿洗い</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>皿洗い</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>休</t>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>皿洗い</t>
+          <t>休</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>皿洗い</t>
+          <t>休</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>皿洗い</t>
+          <t>休</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>皿洗い</t>
+          <t>休</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>皿洗い</t>
+          <t>休</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
@@ -4886,14 +4886,14 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>皿洗い</t>
+          <t>休</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>石橋睦子</t>
+          <t>岡本ますみ</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4903,44 +4903,44 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>皿洗い</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
           <t>皿洗い</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>皿洗い</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>休</t>
@@ -4948,34 +4948,34 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
           <t>皿洗い</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>皿洗い</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
       <c r="R29" t="inlineStr">
         <is>
           <t>休</t>
@@ -4988,7 +4988,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>皿洗い</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>皿洗い</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -5048,14 +5048,14 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>休</t>
+          <t>皿洗い</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>岡本ますみ</t>
+          <t>礒田真祐</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>皿洗い</t>
+          <t>休</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>皿洗い</t>
+          <t>休</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>皿洗い</t>
+          <t>休</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>皿洗い</t>
+          <t>休</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>皿洗い</t>
+          <t>休</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>皿洗い</t>
+          <t>休</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>皿洗い</t>
+          <t>休</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -5217,295 +5217,233 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>礒田真祐</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>休</t>
+          <t>──集計──</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>──集計──</t>
-        </is>
+          <t>早</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>早</t>
+          <t>午前(日+A)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K33" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N33" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O33" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P33" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V33" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="X33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Z33" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AA33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AB33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AC33" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AD33" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AE33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AF33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>午前(日+A)</t>
+          <t>午後(日+P)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E34" t="n">
         <v>7</v>
       </c>
       <c r="F34" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H34" t="n">
         <v>7</v>
@@ -5514,16 +5452,16 @@
         <v>7</v>
       </c>
       <c r="J34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K34" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N34" t="n">
         <v>7</v>
@@ -5532,161 +5470,161 @@
         <v>7</v>
       </c>
       <c r="P34" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S34" t="n">
         <v>7</v>
       </c>
       <c r="T34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V34" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X34" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y34" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z34" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA34" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AB34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD34" t="n">
         <v>7</v>
       </c>
       <c r="AE34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>午後(日+P)</t>
+          <t>準</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N35" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O35" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V35" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y35" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Z35" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AA35" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AB35" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AF35" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>準</t>
+          <t>深</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -5732,7 +5670,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>1</v>
@@ -5753,7 +5691,7 @@
         <v>1</v>
       </c>
       <c r="W36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
         <v>1</v>
@@ -5768,13 +5706,13 @@
         <v>1</v>
       </c>
       <c r="AB36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>1</v>
       </c>
       <c r="AD36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -5786,14 +5724,14 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>深</t>
+          <t>夕・送迎</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
         <v>1</v>
@@ -5802,19 +5740,19 @@
         <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
         <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
         <v>1</v>
@@ -5823,19 +5761,19 @@
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>1</v>
       </c>
       <c r="P37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -5844,19 +5782,19 @@
         <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
         <v>1</v>
       </c>
       <c r="W37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
         <v>1</v>
@@ -5865,121 +5803,21 @@
         <v>1</v>
       </c>
       <c r="AA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>1</v>
       </c>
       <c r="AD37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>夕・送迎</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>1</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
-        <v>1</v>
-      </c>
-      <c r="L38" t="n">
-        <v>1</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="n">
         <v>1</v>
       </c>
     </row>
